--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_metropolitana.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:03</t>
+    <t xml:space="preserve">2026-09-24 00:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -558,13 +558,13 @@
         <v>52</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.59</v>
@@ -598,7 +598,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>52</v>
@@ -607,10 +607,10 @@
         <v>-0.14</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         <v>0.24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>-0.49</v>
@@ -644,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>52</v>
@@ -653,7 +653,7 @@
         <v>0.33</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>-0.65</v>
@@ -667,19 +667,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="8">
@@ -696,13 +696,13 @@
         <v>52</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="9">
@@ -713,19 +713,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="10">
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>47</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.32</v>
@@ -759,19 +759,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.37</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>47</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="12">
@@ -782,7 +782,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>52</v>
@@ -791,10 +791,10 @@
         <v>0.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="13">
@@ -805,16 +805,16 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.51</v>
@@ -828,19 +828,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="15">
@@ -851,7 +851,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>52</v>
@@ -860,10 +860,10 @@
         <v>-0.12</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -880,13 +880,13 @@
         <v>50</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="17">
@@ -903,10 +903,10 @@
         <v>50</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.4</v>
@@ -920,19 +920,19 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="19">
@@ -943,16 +943,16 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.04</v>
@@ -966,19 +966,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>52</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.56</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="21">
@@ -995,10 +995,10 @@
         <v>52</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.19</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_metropolitana.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:53</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_metropolitana.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
